--- a/ig/logoCisis/all-profiles.xlsx
+++ b/ig/logoCisis/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T20:56:02+00:00</t>
+    <t>2024-02-18T21:05:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
